--- a/videos/003_cs_data_science_longitudinal_data_visualization/graficos.xlsx
+++ b/videos/003_cs_data_science_longitudinal_data_visualization/graficos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/content_social_media/data_science/tipos_graficos_dados_em_painel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c308351cf5a860c7/github_oz/oz_youtube/videos/003_cs_data_science_longitudinal_data_visualization/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="288" documentId="11_F25DC773A252ABDACC1048F711DA615C5ADE58F8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{943D2A40-81BB-48FB-871A-41F80E472769}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4147" windowWidth="21600" windowHeight="11333" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="a1" sheetId="1" r:id="rId1"/>
@@ -334,34 +334,34 @@
                   <c:v>188.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>198.66249999999999</c:v>
+                  <c:v>202.66249999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>204.59562500000001</c:v>
+                  <c:v>198.795625</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>219.82540625000001</c:v>
+                  <c:v>189.73540625000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>213.81667656250002</c:v>
+                  <c:v>198.22217656250001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>208.50751039062504</c:v>
+                  <c:v>204.13328539062502</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>198.9328859101563</c:v>
+                  <c:v>205.33994966015629</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>213.87953020566414</c:v>
+                  <c:v>214.60694714316412</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>227.57350671594736</c:v>
+                  <c:v>212.33729450032234</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>222.95218205174473</c:v>
+                  <c:v>226.95415922533846</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>221.09979115433197</c:v>
+                  <c:v>236.30186718660539</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -535,37 +535,37 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>165</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175.25</c:v>
+                  <c:v>163.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>176.01250000000002</c:v>
+                  <c:v>161.255</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>176.81312500000001</c:v>
+                  <c:v>164.31774999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>187.65378125000001</c:v>
+                  <c:v>167.5336375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.03647031250003</c:v>
+                  <c:v>178.910319375</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>192.58829382812505</c:v>
+                  <c:v>188.85583534375002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>197.2177085195313</c:v>
+                  <c:v>194.29862711093753</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>207.07859394550786</c:v>
+                  <c:v>196.01355846648443</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>207.43252364278325</c:v>
+                  <c:v>203.81423638980866</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>207.80414982492243</c:v>
+                  <c:v>213.0049482092991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -739,37 +739,37 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>130</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>138.5</c:v>
+                  <c:v>129.55000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>145.42500000000001</c:v>
+                  <c:v>117.02750000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>141.69625000000002</c:v>
+                  <c:v>110.87887500000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>137.78106250000002</c:v>
+                  <c:v>118.42281875000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>129.67011562500002</c:v>
+                  <c:v>117.34395968750006</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>121.15362140625004</c:v>
+                  <c:v>124.21115767187507</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>126.21130247656255</c:v>
+                  <c:v>113.42171555546884</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>128.52186760039069</c:v>
+                  <c:v>99.092801333242278</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>124.94796098041024</c:v>
+                  <c:v>95.0474413999044</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>134.19535902943076</c:v>
+                  <c:v>82.799813469899618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1123,34 +1123,34 @@
                   <c:v>188.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>198.66249999999999</c:v>
+                  <c:v>202.66249999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>204.59562500000001</c:v>
+                  <c:v>198.795625</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>219.82540625000001</c:v>
+                  <c:v>189.73540625000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>213.81667656250002</c:v>
+                  <c:v>198.22217656250001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>208.50751039062504</c:v>
+                  <c:v>204.13328539062502</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>198.9328859101563</c:v>
+                  <c:v>205.33994966015629</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>213.87953020566414</c:v>
+                  <c:v>214.60694714316412</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>227.57350671594736</c:v>
+                  <c:v>212.33729450032234</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>222.95218205174473</c:v>
+                  <c:v>226.95415922533846</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>221.09979115433197</c:v>
+                  <c:v>236.30186718660539</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1307,37 +1307,37 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>165</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175.25</c:v>
+                  <c:v>163.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>176.01250000000002</c:v>
+                  <c:v>161.255</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>176.81312500000001</c:v>
+                  <c:v>164.31774999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>187.65378125000001</c:v>
+                  <c:v>167.5336375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.03647031250003</c:v>
+                  <c:v>178.910319375</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>192.58829382812505</c:v>
+                  <c:v>188.85583534375002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>197.2177085195313</c:v>
+                  <c:v>194.29862711093753</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>207.07859394550786</c:v>
+                  <c:v>196.01355846648443</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>207.43252364278325</c:v>
+                  <c:v>203.81423638980866</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>207.80414982492243</c:v>
+                  <c:v>213.0049482092991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1494,37 +1494,37 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>130</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>138.5</c:v>
+                  <c:v>129.55000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>145.42500000000001</c:v>
+                  <c:v>117.02750000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>141.69625000000002</c:v>
+                  <c:v>110.87887500000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>137.78106250000002</c:v>
+                  <c:v>118.42281875000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>129.67011562500002</c:v>
+                  <c:v>117.34395968750006</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>121.15362140625004</c:v>
+                  <c:v>124.21115767187507</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>126.21130247656255</c:v>
+                  <c:v>113.42171555546884</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>128.52186760039069</c:v>
+                  <c:v>99.092801333242278</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>124.94796098041024</c:v>
+                  <c:v>95.0474413999044</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>134.19535902943076</c:v>
+                  <c:v>82.799813469899618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2018,10 +2018,10 @@
                   <c:v>188.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>165</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>130</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2148,13 +2148,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>198.66249999999999</c:v>
+                  <c:v>202.66249999999999</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>175.25</c:v>
+                  <c:v>163.1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>138.5</c:v>
+                  <c:v>129.55000000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2281,13 +2281,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>204.59562500000001</c:v>
+                  <c:v>198.795625</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>176.01250000000002</c:v>
+                  <c:v>161.255</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>145.42500000000001</c:v>
+                  <c:v>117.02750000000003</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2414,13 +2414,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>219.82540625000001</c:v>
+                  <c:v>189.73540625000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>176.81312500000001</c:v>
+                  <c:v>164.31774999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>141.69625000000002</c:v>
+                  <c:v>110.87887500000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2547,13 +2547,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>213.81667656250002</c:v>
+                  <c:v>198.22217656250001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>187.65378125000001</c:v>
+                  <c:v>167.5336375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>137.78106250000002</c:v>
+                  <c:v>118.42281875000005</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2685,13 +2685,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>208.50751039062504</c:v>
+                  <c:v>204.13328539062502</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>191.03647031250003</c:v>
+                  <c:v>178.910319375</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>129.67011562500002</c:v>
+                  <c:v>117.34395968750006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2823,13 +2823,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>198.9328859101563</c:v>
+                  <c:v>205.33994966015629</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>192.58829382812505</c:v>
+                  <c:v>188.85583534375002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>121.15362140625004</c:v>
+                  <c:v>124.21115767187507</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2961,13 +2961,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>213.87953020566414</c:v>
+                  <c:v>214.60694714316412</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>197.2177085195313</c:v>
+                  <c:v>194.29862711093753</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>126.21130247656255</c:v>
+                  <c:v>113.42171555546884</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3099,13 +3099,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>227.57350671594736</c:v>
+                  <c:v>212.33729450032234</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>207.07859394550786</c:v>
+                  <c:v>196.01355846648443</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>128.52186760039069</c:v>
+                  <c:v>99.092801333242278</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3237,13 +3237,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>222.95218205174473</c:v>
+                  <c:v>226.95415922533846</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>207.43252364278325</c:v>
+                  <c:v>203.81423638980866</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>124.94796098041024</c:v>
+                  <c:v>95.0474413999044</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3375,13 +3375,13 @@
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>221.09979115433197</c:v>
+                  <c:v>236.30186718660539</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>207.80414982492243</c:v>
+                  <c:v>213.0049482092991</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>134.19535902943076</c:v>
+                  <c:v>82.799813469899618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3725,34 +3725,34 @@
                   <c:v>188.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>198.66249999999999</c:v>
+                  <c:v>202.66249999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>204.59562500000001</c:v>
+                  <c:v>198.795625</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>219.82540625000001</c:v>
+                  <c:v>189.73540625000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>213.81667656250002</c:v>
+                  <c:v>198.22217656250001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>208.50751039062504</c:v>
+                  <c:v>204.13328539062502</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>198.9328859101563</c:v>
+                  <c:v>205.33994966015629</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>213.87953020566414</c:v>
+                  <c:v>214.60694714316412</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>227.57350671594736</c:v>
+                  <c:v>212.33729450032234</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>222.95218205174473</c:v>
+                  <c:v>226.95415922533846</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>221.09979115433197</c:v>
+                  <c:v>236.30186718660539</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3910,37 +3910,37 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>165</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175.25</c:v>
+                  <c:v>163.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>176.01250000000002</c:v>
+                  <c:v>161.255</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>176.81312500000001</c:v>
+                  <c:v>164.31774999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>187.65378125000001</c:v>
+                  <c:v>167.5336375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.03647031250003</c:v>
+                  <c:v>178.910319375</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>192.58829382812505</c:v>
+                  <c:v>188.85583534375002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>197.2177085195313</c:v>
+                  <c:v>194.29862711093753</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>207.07859394550786</c:v>
+                  <c:v>196.01355846648443</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>207.43252364278325</c:v>
+                  <c:v>203.81423638980866</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>207.80414982492243</c:v>
+                  <c:v>213.0049482092991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4098,37 +4098,37 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>130</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>138.5</c:v>
+                  <c:v>129.55000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>145.42500000000001</c:v>
+                  <c:v>117.02750000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>141.69625000000002</c:v>
+                  <c:v>110.87887500000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>137.78106250000002</c:v>
+                  <c:v>118.42281875000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>129.67011562500002</c:v>
+                  <c:v>117.34395968750006</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>121.15362140625004</c:v>
+                  <c:v>124.21115767187507</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>126.21130247656255</c:v>
+                  <c:v>113.42171555546884</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>128.52186760039069</c:v>
+                  <c:v>99.092801333242278</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>124.94796098041024</c:v>
+                  <c:v>95.0474413999044</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>134.19535902943076</c:v>
+                  <c:v>82.799813469899618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4469,34 +4469,34 @@
                   <c:v>188.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>198.66249999999999</c:v>
+                  <c:v>202.66249999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>204.59562500000001</c:v>
+                  <c:v>198.795625</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>219.82540625000001</c:v>
+                  <c:v>189.73540625000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>213.81667656250002</c:v>
+                  <c:v>198.22217656250001</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>208.50751039062504</c:v>
+                  <c:v>204.13328539062502</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>198.9328859101563</c:v>
+                  <c:v>205.33994966015629</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>213.87953020566414</c:v>
+                  <c:v>214.60694714316412</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>227.57350671594736</c:v>
+                  <c:v>212.33729450032234</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>222.95218205174473</c:v>
+                  <c:v>226.95415922533846</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>221.09979115433197</c:v>
+                  <c:v>236.30186718660539</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4653,37 +4653,37 @@
                   <c:v>160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>165</c:v>
+                  <c:v>162</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>175.25</c:v>
+                  <c:v>163.1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>176.01250000000002</c:v>
+                  <c:v>161.255</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>176.81312500000001</c:v>
+                  <c:v>164.31774999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>187.65378125000001</c:v>
+                  <c:v>167.5336375</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>191.03647031250003</c:v>
+                  <c:v>178.910319375</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>192.58829382812505</c:v>
+                  <c:v>188.85583534375002</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>197.2177085195313</c:v>
+                  <c:v>194.29862711093753</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>207.07859394550786</c:v>
+                  <c:v>196.01355846648443</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>207.43252364278325</c:v>
+                  <c:v>203.81423638980866</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>207.80414982492243</c:v>
+                  <c:v>213.0049482092991</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4840,37 +4840,37 @@
                   <c:v>120</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>130</c:v>
+                  <c:v>131</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>138.5</c:v>
+                  <c:v>129.55000000000001</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>145.42500000000001</c:v>
+                  <c:v>117.02750000000003</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>141.69625000000002</c:v>
+                  <c:v>110.87887500000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>137.78106250000002</c:v>
+                  <c:v>118.42281875000005</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>129.67011562500002</c:v>
+                  <c:v>117.34395968750006</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>121.15362140625004</c:v>
+                  <c:v>124.21115767187507</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>126.21130247656255</c:v>
+                  <c:v>113.42171555546884</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>128.52186760039069</c:v>
+                  <c:v>99.092801333242278</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>124.94796098041024</c:v>
+                  <c:v>95.0474413999044</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>134.19535902943076</c:v>
+                  <c:v>82.799813469899618</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8412,43 +8412,43 @@
       </c>
       <c r="H3" s="2">
         <f t="shared" ref="H3:Q3" ca="1" si="0">(1+$C3)*G3 + RANDBETWEEN($A3,$B3)</f>
-        <v>198.66249999999999</v>
+        <v>202.66249999999999</v>
       </c>
       <c r="I3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>204.59562500000001</v>
+        <v>198.795625</v>
       </c>
       <c r="J3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>219.82540625000001</v>
+        <v>189.73540625000001</v>
       </c>
       <c r="K3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>213.81667656250002</v>
+        <v>198.22217656250001</v>
       </c>
       <c r="L3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>208.50751039062504</v>
+        <v>204.13328539062502</v>
       </c>
       <c r="M3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>198.9328859101563</v>
+        <v>205.33994966015629</v>
       </c>
       <c r="N3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>213.87953020566414</v>
+        <v>214.60694714316412</v>
       </c>
       <c r="O3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>227.57350671594736</v>
+        <v>212.33729450032234</v>
       </c>
       <c r="P3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>222.95218205174473</v>
+        <v>226.95415922533846</v>
       </c>
       <c r="Q3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>221.09979115433197</v>
+        <v>236.30186718660539</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -8469,47 +8469,47 @@
       </c>
       <c r="G4" s="2">
         <f t="shared" ref="G4:Q5" ca="1" si="1">(1+$C4)*F4 + RANDBETWEEN($A4,$B4)</f>
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>175.25</v>
+        <v>163.1</v>
       </c>
       <c r="I4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>176.01250000000002</v>
+        <v>161.255</v>
       </c>
       <c r="J4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>176.81312500000001</v>
+        <v>164.31774999999999</v>
       </c>
       <c r="K4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>187.65378125000001</v>
+        <v>167.5336375</v>
       </c>
       <c r="L4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>191.03647031250003</v>
+        <v>178.910319375</v>
       </c>
       <c r="M4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>192.58829382812505</v>
+        <v>188.85583534375002</v>
       </c>
       <c r="N4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>197.2177085195313</v>
+        <v>194.29862711093753</v>
       </c>
       <c r="O4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>207.07859394550786</v>
+        <v>196.01355846648443</v>
       </c>
       <c r="P4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>207.43252364278325</v>
+        <v>203.81423638980866</v>
       </c>
       <c r="Q4" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>207.80414982492243</v>
+        <v>213.0049482092991</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="29.25" customHeight="1" x14ac:dyDescent="0.45">
@@ -8530,47 +8530,47 @@
       </c>
       <c r="G5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>138.5</v>
+        <v>129.55000000000001</v>
       </c>
       <c r="I5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>145.42500000000001</v>
+        <v>117.02750000000003</v>
       </c>
       <c r="J5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>141.69625000000002</v>
+        <v>110.87887500000004</v>
       </c>
       <c r="K5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>137.78106250000002</v>
+        <v>118.42281875000005</v>
       </c>
       <c r="L5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>129.67011562500002</v>
+        <v>117.34395968750006</v>
       </c>
       <c r="M5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>121.15362140625004</v>
+        <v>124.21115767187507</v>
       </c>
       <c r="N5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>126.21130247656255</v>
+        <v>113.42171555546884</v>
       </c>
       <c r="O5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>128.52186760039069</v>
+        <v>99.092801333242278</v>
       </c>
       <c r="P5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>124.94796098041024</v>
+        <v>95.0474413999044</v>
       </c>
       <c r="Q5" s="2">
         <f t="shared" ca="1" si="1"/>
-        <v>134.19535902943076</v>
+        <v>82.799813469899618</v>
       </c>
     </row>
   </sheetData>
